--- a/artfynd/A 55298-2024 artfynd.xlsx
+++ b/artfynd/A 55298-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820570</v>
+        <v>121149935</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509556</v>
+        <v>509621</v>
       </c>
       <c r="R2" t="n">
-        <v>6881558</v>
+        <v>6881643</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820571</v>
+        <v>119820569</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,7 +823,7 @@
         <v>509543</v>
       </c>
       <c r="R3" t="n">
-        <v>6881563</v>
+        <v>6881506</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,37 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149935</v>
+        <v>119820570</v>
       </c>
       <c r="B4" t="n">
-        <v>78343</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,13 +926,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509621</v>
+        <v>509556</v>
       </c>
       <c r="R4" t="n">
-        <v>6881643</v>
+        <v>6881558</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1005,6 +990,112 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>119820571</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Storåströmmen, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>509543</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6881563</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55298-2024 artfynd.xlsx
+++ b/artfynd/A 55298-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149935</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820569</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820570</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,8 +1116,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820571</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>